--- a/www/download/COUNTRY.BGR.zdW13.xlsx
+++ b/www/download/COUNTRY.BGR.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Bulgaria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0671456399048756</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.129019769453539</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.55465380102638</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.75697525069061</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.83398739185676</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.11747769546194</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.18321545619096</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0705219732609</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.72965500230581</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.5735146527652</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.57168460694959</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.55789934671618</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.42700168561391</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.33054449933994</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.4031148969898</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.519</t>
+          <t>1.65491879138928</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.614</t>
+          <t>2.08038308932218</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.48442944376938</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.472</t>
+          <t>1.44619295855625</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.312</t>
+          <t>1.62433340304938</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.239</t>
+          <t>1.53846747871379</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.215</t>
+          <t>1.46152668977426</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.222</t>
+          <t>1.41689320032648</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3.317</t>
+          <t>2.11571813813313</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.404</t>
+          <t>1.53191681406483</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>1.60112491568941</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.612</t>
+          <t>1.69767423334085</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3.727</t>
+          <t>1.6973900872426</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.40821051216524</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>1.24842912228583</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>2.77271716672977</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>3.33216571636054</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>3.92640171089035</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.528</t>
+          <t>2.69678656530257</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.03520572644091</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>3.11795617098477</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.272</t>
+          <t>2.98629493787331</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.281</t>
+          <t>3.14190760520639</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.365</t>
+          <t>4.65595222503249</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.432</t>
+          <t>3.21997566011351</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>3.39946013316828</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.631</t>
+          <t>3.55868056770798</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.53542265340509</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.817</t>
+          <t>3.1849853632524</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.724</t>
+          <t>2.83210436652448</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6025.009</t>
+          <t>3.55894483336728</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6178.773</t>
+          <t>4.07233366386645</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5980.411</t>
+          <t>4.65410580753296</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5727.669</t>
+          <t>3.68125224502331</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5532.414</t>
+          <t>4.27958038860362</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5313.109</t>
+          <t>4.57964326817037</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5310.295</t>
+          <t>4.54561664129907</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5320.554</t>
+          <t>4.778606857481</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5442.215</t>
+          <t>4.00600968861281</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5662.196</t>
+          <t>5.12325029025554</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>5797.413</t>
+          <t>5.39010070620185</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5998.505</t>
+          <t>5.64856678587077</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6165.971</t>
+          <t>5.34520949321187</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6241.306</t>
+          <t>5.1594405285221</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6207.343</t>
+          <t>4.60893756198279</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4763.822</t>
+          <t>6886955600.59111</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4804.766</t>
+          <t>7207419430.47789</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4583.11</t>
+          <t>6621462795.71029</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4317.376</t>
+          <t>6296944084.28997</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4123.538</t>
+          <t>5882478936.91973</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3934.009</t>
+          <t>5597377149.48479</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3898.358</t>
+          <t>5357934462.9873</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3902.291</t>
+          <t>5286838548.4719</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4004.834</t>
+          <t>5456875614.92465</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4138.132</t>
+          <t>5857148145.41522</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4244.756</t>
+          <t>5969681513.77597</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4411.226</t>
+          <t>6339592950.38071</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4582.662</t>
+          <t>6529870999.79063</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4717.103</t>
+          <t>6522589139.63906</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4560.187</t>
+          <t>6411182500.71277</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>1162223969.77101</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>1043377364.23131</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>883839296.762013</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>1039554711.89317</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>900495307.596942</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>829410228.931969</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>835884722.328003</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>812521416.687691</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>838569927.049767</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>851100669.330575</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>842592586.500679</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>845553530.985253</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>906513377.633545</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>999766975.424833</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>1066677377.33329</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>8514297.85252811</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>8074413.3508796</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>9492952.42907177</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>8532605.59845383</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>7599459.08579626</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>7319890.57516607</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>6503745.56576759</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>5663222.10413044</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>4278721.91622585</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>3655451.66738627</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>3387391.95792091</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>3054773.41060673</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>2449566.04412119</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>2095527.04882165</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>2189777.18715877</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>34866.7740127224</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>35607.677201446</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>34383.3435262634</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>32592.0983691085</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>32029.4795810262</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>31263.9017713637</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>29239.4390575032</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>29848.7495322741</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>32091.9982242635</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>36246.7161200586</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>39596.4415338551</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>42637.0002312147</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>49117.3830728636</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>53005.515300034</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>48140.3440864817</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>59341.2365609674</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>62547.0184568001</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>57277.6507111347</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>53920.9826277721</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>52395.1014816449</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>50680.1383089923</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>47114.0419736099</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>47503.6731856775</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>52563.5069137119</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>62056.1660977286</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>67742.795777054</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>75103.1652257705</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>87161.567497448</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>95319.4413484451</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>87339.2714196931</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>3.09888456920238</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>3.60501293409479</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>4.18545622895827</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>3.15310172653198</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>3.57918824262452</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>3.74314020103878</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>3.66375074919754</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>3.80269309811919</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>3.7757901527541</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>3.86209463711832</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>4.03773243202701</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>4.21696833890572</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>4.05526078516649</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>3.71820257428149</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>3.27513257333647</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0671456399048756</t>
+          <t>428.357590127368</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.129019769453539</t>
+          <t>381.739932941</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.55465380102638</t>
+          <t>341.235006560395</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.75697525069061</t>
+          <t>411.17257448021</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.83398739185676</t>
+          <t>376.756689604975</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.11747769546194</t>
+          <t>356.658881501599</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.18321545619096</t>
+          <t>367.858435210141</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.0705219732609</t>
+          <t>356.275285752737</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.72965500230581</t>
+          <t>354.545039341183</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.5735146527652</t>
+          <t>349.959156797111</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.57168460694959</t>
+          <t>334.004275776224</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.55789934671618</t>
+          <t>321.381045604429</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.42700168561391</t>
+          <t>330.808078543789</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.33054449933994</t>
+          <t>354.879659031958</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.4031148969898</t>
+          <t>391.656830304128</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-458523239.245992</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-563737715.93534</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-845280425.018433</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-723418911.963051</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-721487975.672382</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-696465152.526557</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-605795174.101439</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-664924991.146206</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-642217467.780256</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-605492331.540502</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>-649677004.929545</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-648740836.696304</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-670242712.788686</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-546693072.010724</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-286938852.287435</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-480907567.842798</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-606087246.325724</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-865561974.094201</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-734188700.189233</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-725582354.642676</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-712470086.149567</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-688707241.18064</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-767823558.556497</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>-753574988.877203</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-744669311.632405</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-757614523.577078</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-828825110.509612</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-828746382.197351</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-668273442.784984</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-448864080.143404</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>22384328.5968066</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>42349530.3903839</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>20281549.0757674</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>10769788.226182</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>4094378.97029365</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>16004933.62301</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>82912067.0792016</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>102898567.410291</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>111357521.096947</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>139176980.091903</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>107937518.647533</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>180084273.813308</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>158503669.408664</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>121580370.77426</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>161925227.855969</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1755.78831627379</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1757.91732865378</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1769.45919030721</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1707.64152897636</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1725.23980336924</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1691.68307890776</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1715.60005280993</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1711.08085591511</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1693.23270759344</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>1701.53453947368</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1682.62417251358</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>1676.63473964272</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>1672.32110687869</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1674.39412080472</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>1674.38487280289</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1712.24910236074</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1709.79175195496</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1708.44720906348</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1649.43837379205</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1670.20912323346</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1640.20282159726</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1651.82748538012</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1651.21780150208</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1640.50611925001</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1663.63919494638</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1658.67847333486</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1660.71566998893</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1654.58353458917</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>1660.09552792094</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1659.82599798028</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>165.49</t>
+          <t>5721.26684707971</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>208.04</t>
+          <t>7358.52060140411</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>248.44</t>
+          <t>6196.35018071592</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>144.62</t>
+          <t>5779.99963217886</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>162.43</t>
+          <t>6949.75614597142</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>153.85</t>
+          <t>6339.86696377089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>146.15</t>
+          <t>6298.97003500614</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>141.69</t>
+          <t>7064.93906070471</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>211.57</t>
+          <t>9391.07357302661</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>153.19</t>
+          <t>12285.3479543285</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>160.11</t>
+          <t>10701.9758549452</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>169.77</t>
+          <t>15598.6154976521</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>169.74</t>
+          <t>23672.799380887</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>140.82</t>
+          <t>28533.0144010217</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>124.84</t>
+          <t>21725.163896309</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>277.27</t>
+          <t>1329253869.37849</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>333.22</t>
+          <t>1625468221.55644</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>392.64</t>
+          <t>1577781025.9793</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>269.68</t>
+          <t>1468556770.38147</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>303.52</t>
+          <t>1691234553.64986</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>311.8</t>
+          <t>1432572554.88186</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>298.63</t>
+          <t>1232591814.15562</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>314.19</t>
+          <t>1343170368.94961</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>465.6</t>
+          <t>1399620119.88922</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>1515460814.53749</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>339.95</t>
+          <t>1212179549.07755</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>355.87</t>
+          <t>1513273285.60937</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>353.54</t>
+          <t>1720891830.41323</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>1895309955.21408</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>283.21</t>
+          <t>1666617393.81224</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>355.89</t>
+          <t>5490.23842158157</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>407.23</t>
+          <t>6176.15579939194</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>465.41</t>
+          <t>5302.77511120537</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>368.13</t>
+          <t>5314.21712516818</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>427.96</t>
+          <t>7204.36396197689</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>457.96</t>
+          <t>6601.36411143601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>454.56</t>
+          <t>7146.01509412255</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>477.86</t>
+          <t>7993.22441665403</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>400.6</t>
+          <t>10928.7375165054</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>512.33</t>
+          <t>14474.4025210414</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>539.01</t>
+          <t>14190.5286717511</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>564.86</t>
+          <t>20576.4268715346</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>534.52</t>
+          <t>30675.4328324775</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>515.94</t>
+          <t>37860.2439430891</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>460.89</t>
+          <t>24912.5895408874</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6025.009</t>
+          <t>838890471.355658</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6178.773</t>
+          <t>905435556.227575</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5980.411</t>
+          <t>624370999.284411</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5727.669</t>
+          <t>685352644.131066</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5532.414</t>
+          <t>1003195279.48337</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5313.109</t>
+          <t>770891441.659308</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5310.295</t>
+          <t>745509481.430685</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5320.554</t>
+          <t>806900720.174684</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5442.215</t>
+          <t>959873155.294205</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5662.196</t>
+          <t>1175055359.57127</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>5797.413</t>
+          <t>953750543.733516</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>5998.505</t>
+          <t>1375144478.32126</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6165.971</t>
+          <t>1686396604.68402</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6241.306</t>
+          <t>2110961359.00033</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6207.343</t>
+          <t>1666584247.68142</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4763.822</t>
+          <t>231.028425498138</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4804.766</t>
+          <t>1182.36480201217</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4583.11</t>
+          <t>893.575069510543</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4317.376</t>
+          <t>465.782507010675</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4123.538</t>
+          <t>-254.607816005468</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3934.009</t>
+          <t>-261.497147665119</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3898.358</t>
+          <t>-847.045059116402</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3902.291</t>
+          <t>-928.285355949323</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4004.834</t>
+          <t>-1537.66394347881</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4138.132</t>
+          <t>-2189.05456671294</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>4244.756</t>
+          <t>-3488.55281680589</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4411.226</t>
+          <t>-4977.81137388255</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4582.662</t>
+          <t>-7002.63345159048</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>4717.103</t>
+          <t>-9327.22954206735</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4560.187</t>
+          <t>-3187.42564457845</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6886.956</t>
+          <t>490363398.022828</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7207.419</t>
+          <t>720032665.32886</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6621.463</t>
+          <t>953410026.69489</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6296.944</t>
+          <t>783204126.250407</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5882.479</t>
+          <t>688039274.166487</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5597.377</t>
+          <t>661681113.22255</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5357.934</t>
+          <t>487082332.724939</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5286.839</t>
+          <t>536269648.774928</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5456.876</t>
+          <t>439746964.595016</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5857.148</t>
+          <t>340405454.966226</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>5969.682</t>
+          <t>258429005.344034</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6339.593</t>
+          <t>138128807.288114</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>6529.871</t>
+          <t>34495225.7292072</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>6522.589</t>
+          <t>-215651403.786252</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>6411.183</t>
+          <t>33146.1308249253</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>7012.30761</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>6877.74777</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>6270.65211</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>6914.69346</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>6670.10395</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>6416.64399</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>6743.30415</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>7429.86574</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>9358.55309</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>11103.62409</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>11861.38017</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>13600.24546</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>17476.37378</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>20824.95179</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>19526.1047</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4046.527</t>
+          <t>0.0961626549542137</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4103.145</t>
+          <t>0.0946647106938832</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3974.814</t>
+          <t>0.0877570833296613</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3806.137</t>
+          <t>0.089969681133787</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3595.999</t>
+          <t>0.098120384100409</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3452.947</t>
+          <t>0.114549970871878</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3325.187</t>
+          <t>0.118559557672574</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3321.965</t>
+          <t>0.12371598528813</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3331.628</t>
+          <t>0.122971255884516</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3421.133</t>
+          <t>0.124822868039856</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3489.347</t>
+          <t>0.118375593986645</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3599.066</t>
+          <t>0.121232619707733</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3679.72</t>
+          <t>0.12380559932568</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3627.101</t>
+          <t>0.111491454534325</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3533.766</t>
+          <t>0.0994897021569957</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>5489.46630861788</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>5006.89951687757</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>3785.66597417408</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>4945.03266376072</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>4798.34269918028</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>4380.49479616497</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>4758.44007447194</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>5335.1763633511</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>6958.43965857143</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>8259.53538536535</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>9075.80306826029</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>10152.1320669268</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>13383.0860932627</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>17345.3482740352</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>17471.3095980248</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1162.224</t>
+          <t>6607.49241501291</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1043.377</t>
+          <t>6217.29677098901</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>883.839</t>
+          <t>4798.85981629446</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1039.555</t>
+          <t>6259.01049800769</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>900.495</t>
+          <t>6036.95211304725</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>829.41</t>
+          <t>5484.63915254219</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>835.885</t>
+          <t>5928.87398593274</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>812.521</t>
+          <t>6628.1048903259</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>838.57</t>
+          <t>8671.86455135768</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>851.101</t>
+          <t>10430.9043908861</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>842.593</t>
+          <t>11518.9534811051</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>845.554</t>
+          <t>12840.3745381041</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>906.513</t>
+          <t>16776.530543474</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>999.767</t>
+          <t>21718.3063310489</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1066.677</t>
+          <t>22406.6496559926</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>309.89</t>
+          <t>59355.9918630032</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>360.5</t>
+          <t>69181.360625382</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>418.55</t>
+          <t>57565.0534638733</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>315.31</t>
+          <t>57282.9470666745</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>357.92</t>
+          <t>56099.0221085957</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>374.31</t>
+          <t>49644.40832393</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>366.38</t>
+          <t>51815.9310363921</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>380.27</t>
+          <t>56629.2617187464</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>377.58</t>
+          <t>69005.7104614056</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>386.21</t>
+          <t>81828.1596914803</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>403.77</t>
+          <t>94664.9996971436</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>421.7</t>
+          <t>108329.971368739</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>405.53</t>
+          <t>134829.532811473</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>371.82</t>
+          <t>171064.196342325</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>327.51</t>
+          <t>169178.186375985</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8.514</t>
+          <t>6607.49241501291</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.074</t>
+          <t>5584.61395596881</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.493</t>
+          <t>5355.12594675398</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>8.533</t>
+          <t>6252.61889475759</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7.599</t>
+          <t>6075.67002837942</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>5928.32673597345</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.504</t>
+          <t>6194.74997422339</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>5.663</t>
+          <t>6389.92025212374</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4.279</t>
+          <t>6725.03702834154</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.655</t>
+          <t>7048.28016969507</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3.387</t>
+          <t>7484.59364170855</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3.055</t>
+          <t>7785.80118759571</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>8447.78820222002</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.096</t>
+          <t>9793.18926755484</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>11135.2774240175</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5489.46630861788</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4474.00496783007</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4351.7116477922</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4818.72925768776</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4544.72734306569</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4475.68133504424</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4735.73989088866</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>4844.02819302775</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5039.88997323793</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>5141.88656144408</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>5458.5149271311</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5602.33644205346</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6254.31714764814</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7238.47960290336</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>7446.98105217487</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5707.82976498709</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>6549.03348901099</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>5051.74119370554</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>5153.72848199231</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>5504.45759695275</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5686.76552745781</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6143.27386406726</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>7005.9449096741</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>8485.71887864231</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>10214.0255791139</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11206.0255688949</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>13133.1262218959</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>16692.651116526</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>19072.1960689511</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>16831.4873740074</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4763821895.65152</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4804766257.4269</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4583109986.79267</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4317376468.78796</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4123537525.08647</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3934009000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3898358000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3902291000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4004834000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4138132000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4244756000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4411226000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4582661529.17968</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>4717103117.13106</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4560187201.07867</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6025008671.9305</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6178772891.40574</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5980411261.78583</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5727669207.89169</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>5532413588.31211</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5313109000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5310295000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5320554000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>5442215000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>5662196000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>5797413000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5998505000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6165971000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6241305983.29216</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6207342931.12282</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4046527144.99397</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4103144656.09807</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3974814384.40038</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3806136517.14592</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3595999123.3511</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3452947352.11324</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3325186964.26779</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3321964578.06737</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3331627831.29498</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3421132813.22682</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3489347351.61952</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3599065702.20611</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3679720139.52698</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3627100553.10887</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3533765814.26293</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3518768.77238457</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3613757.57272251</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3500495.20410063</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3472496.63818831</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3312407.71670649</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3239300</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3214800</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3222200</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3317400</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3403500</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3495200</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3612000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3726600</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3759606.5276488</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3739755.21450808</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2713209.70272858</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2733215.13993289</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2590119.06683022</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2528268.60645396</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2390124.26970069</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2325500</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2272300</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2280600</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2365200</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2432000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2522700</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2631000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2740300</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2817200</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2723500</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6025008671.9305</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6178772891.40574</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5980411261.78583</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5727669207.89169</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5532413588.31211</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5313109000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5310295000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5320554000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5442215000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5662196000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5797413000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5998505000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6165971000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6241305983.29216</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6207342931.12282</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4763821895.65152</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4804766257.4269</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4583109986.79267</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4317376468.78796</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4123537525.08647</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3934009000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3898358000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3902291000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4004834000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4138132000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4244756000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4411226000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4582661529.17968</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4717103117.13106</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4560187201.07867</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0785096043442988</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0783260088229312</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0725635829408859</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0671800623138325</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0688251783923756</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0699078324120806</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0692388796418979</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0724385050920685</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0880048178129122</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0921735966508009</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0974095903387319</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.101508629331494</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.105364824723641</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.115065358467651</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.120196730948339</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.149374382655247</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.155770502716519</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.148432965518307</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.141043625728438</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.152727722560584</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.156792418524991</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.163142546644421</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.162375411188584</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.16653267978683</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.175757286429952</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.179013652283156</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.187159780642293</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.182028895279162</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.18440883981998</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.202179913289584</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.772116013000455</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.76590348846055</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.779003451540807</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.79177631195773</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.77844709904704</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.773299749062929</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.767618573713681</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.765186083719348</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.745462502400258</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.732069116919247</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.723576757378112</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.711331590026213</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.712606279997197</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.700525801712369</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.677623355762077</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>28401.43623</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>30820.60983</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>24225.98663</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>25554.54324</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>25628.093</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>25699.58624</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>27780.08002</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>31008.8956</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>40492.17933</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>51515.12221</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>59695.11906</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>71335.35282</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>92537.04128</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>110695.73757</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>106237.58348</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>12315.32218</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>12766.33026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>9850.60101</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>11412.73898</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>11541.40971</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>11171.40468</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>12072.14785</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>13634.0498</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>17157.58343</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>20644.92997</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>22724.97905</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>25973.50076</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>33469.18166</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>40790.5024</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>39238.13703</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3985.49606034859</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3959.94442489811</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3912.92233580997</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3897.84900789496</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3908.98421005755</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>3942.36819554376</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4007.15957625372</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4082.12838080333</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>4178.98220818302</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>4301.6328803054</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4499.12178577914</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>4729.83595275513</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>4992.82783053041</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>5336.88681506164</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>5500.80095714951</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
